--- a/docs/data/jp/xlsx/6382.xlsx
+++ b/docs/data/jp/xlsx/6382.xlsx
@@ -1156,7 +1156,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>설비 부문</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -1438,7 +1438,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>자동차부품 부문</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -8245,7 +8245,7 @@
     <row r="123">
       <c r="A123" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>설비 부문 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C123" s="20" t="n">
@@ -8297,7 +8297,7 @@
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>자동차부품 부문 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C124" s="20" t="n">
@@ -8505,7 +8505,7 @@
     <row r="128">
       <c r="A128" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>설비 부문 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C128" s="20" t="n">
@@ -8557,7 +8557,7 @@
     <row r="129">
       <c r="A129" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>자동차부품 부문 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C129" s="20" t="n">
@@ -8765,7 +8765,7 @@
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>설비 부문 · 계</t>
         </is>
       </c>
       <c r="C133" s="20" t="n">
@@ -8817,7 +8817,7 @@
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>자동차부품 부문 · 계</t>
         </is>
       </c>
       <c r="C134" s="20" t="n">
@@ -9025,7 +9025,7 @@
     <row r="138">
       <c r="A138" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>설비 부문 · 부문 이익</t>
         </is>
       </c>
       <c r="C138" s="20" t="n">
@@ -9077,7 +9077,7 @@
     <row r="139">
       <c r="A139" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>자동차부품 부문 · 부문 이익</t>
         </is>
       </c>
       <c r="C139" s="20" t="n">
@@ -9981,7 +9981,7 @@
     <row r="158">
       <c r="A158" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Warranties For Completed Construction Ope CF</t>
+          <t>완성공사 보증 충당금 증감액</t>
         </is>
       </c>
       <c r="E158" s="20" t="n">
@@ -15491,7 +15491,7 @@
     <row r="118">
       <c r="A118" s="18" t="inlineStr">
         <is>
-          <t>Provision For Warranties For Completed Construction</t>
+          <t>완성공사 보증 충당금</t>
         </is>
       </c>
       <c r="C118" s="20" t="n">
@@ -15528,7 +15528,7 @@
     <row r="119">
       <c r="A119" s="18" t="inlineStr">
         <is>
-          <t>Notes Payable Facilities</t>
+          <t>설비관련 지급어음</t>
         </is>
       </c>
       <c r="H119" s="20" t="n">
